--- a/evaluation/multiple_choice_qa/MMLU-college_medicine/qwen2.5_trained/fa_qwn_result.xlsx
+++ b/evaluation/multiple_choice_qa/MMLU-college_medicine/qwen2.5_trained/fa_qwn_result.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA8118E0-E7BF-4F26-A266-001CAE646795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC2D9989-E6E3-4C16-95F8-E050A8BD873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1347,6 +1347,9 @@
      \frac{84 \text{ گرم}}{28 \text{ گرم/مول}} = 3 \text{ م</t>
   </si>
   <si>
+    <t>invalid</t>
+  </si>
+  <si>
     <t>استفاده از سونا، که گاهی به آن "حمام سونا" نیز گفته می‌شود، با قرار گرفتن کوتاه‌مدت و غیرفعال در معرض گرمای شدید مشخص می‌شود. این قرارگیری در معرض گرما باعث ایجاد هایپرترمی خفیف (افزایش دمای مرکزی بدن) می‌شود که پاسخ تنظیم حرارتی را تحریک می‌کند. این پاسخ شامل مکانیسم‌های نورواندوکرین (عصبی-هورمونی)، قلبی-عروقی و محافظت سلولی است که با همکاری هم هموستاز (تعادل داخلی بدن) را بازگردانده و بدن را برای مواجهه با استرس‌های گرمایی آینده آماده می‌کنند... در دهه‌های اخیر، حمام سونا به عنوان روشی برای افزایش طول عمر و بهبود سلامت کلی مطرح شده است، که بر اساس داده‌های قانع‌کننده از مطالعات مشاهده‌ای، مداخله‌ای و مکانیکی است. یافته‌های مطالعات شرکت‌کنندگان در مطالعه عوامل خطر بیماری ایسکمیک قلب کوپیو (KIHD)، که یک مطالعه کوهورت آینده‌نگر مبتنی بر جمعیت در مورد نتایج سلامت در بیش از ۲۳۰۰ مرد میانسال از شرق فنلاند است، ارتباط قوی بین استفاده از سونا و کاهش مرگ و بیماری را نشان داده است... یافته‌های KIHD نشان دادند مردانی که دو تا سه بار در هفته از سونا استفاده می‌کردند، ۲۷ درصد کمتر در معرض مرگ ناشی از علل قلبی-عروقی بودند نسبت به مردانی که از سونا استفاده نمی‌کردند.[۲] علاوه بر این، مزایای مشاهده‌شده وابسته به دوز بود: مردانی که تقریباً دو برابر بیشتر (چهار تا هفت بار در هفته) از سونا استفاده می‌کردند، تقریباً دو برابر مزایا را تجربه کرده و ۵۰ درصد کمتر در معرض مرگ ناشی از علل قلبی-عروقی بودند.[۲] همچنین، کاربران مکرر سونا ۴۰ درصد کمتر در معرض مرگ زودرس به هر دلیلی بودند. این یافته‌ها حتی پس از در نظر گرفتن سن، سطح فعالیت و عوامل سبک زندگی که ممکن بود بر سلامت مردان تأثیر بگذارند، همچنان معتبر باقی ماندند.[۲]... مطالعه KIHD همچنین نشان داد که استفاده مکرر از سونا خطر ابتلا به زوال عقل و بیماری آلزایمر را به صورت وابسته به دوز کاهش می‌دهد. مردانی که دو تا سه بار در هفته از سونا استفاده می‌کردند، ۶۶ درصد خطر کمتری برای ابتلا به زوال عقل و ۶۵ درصد خطر کمتری برای ابتلا به بیماری آلزایمر داشتند، در مقایسه با مردانی که فقط یک بار در هفته از سونا استفاده می‌کردند... مزایای سلامتی مرتبط با استفاده از سونا به سایر جنبه‌های سلامت روان نیز گسترش یافت. مردانی که در مطالعه KIHD شرکت کرده و چهار تا هفت بار در هفته از سونا استفاده می‌کردند، ۷۷ درصد کمتر در معرض ابتلا به اختلالات روان‌پریشی بودند، بدون توجه به عادات غذایی، وضعیت اقتصادی-اجتماعی، فعالیت بدنی و وضعیت التهابی (که با پروتئین واکنشی C اندازه‌گیری شد)... قرار گرفتن در معرض دمای بالا بدن را تحت استرس قرار می‌دهد و باعث ایجاد یک پاسخ سریع و قوی می‌شود. دمای پوست و دمای مرکزی بدن به طور قابل توجهی افزایش می‌یابد و تعریق آغاز می‌شود. ابتدا پوست گرم می‌شود و به ۴۰ درجه سانتیگراد (۱۰۴ درجه فارنهایت) می‌رسد، سپس تغییرات در دمای مرکزی بدن رخ می‌دهد که به آرامی از ۳۷ درجه سانتیگراد (۹۸.۶ درجه فارنهایت، یا حالت طبیعی) به ۳۸ درجه سانتیگراد (۱۰۰.۴ درجه فارنهایت) افزایش یافته و سپس به سرعت به ۳۹ درجه سانتیگراد (۱۰۲.۲ درجه فارنهایت) می‌رسد... برون‌ده قلبی، که معیاری از میزان کار قلب در پاسخ به نیاز بدن به اکسیژن است، ۶۰ تا ۷۰ درصد افزایش می‌یابد، در حالی که ضربان قلب (تعداد ضربان در دقیقه) افزایش یافته و حجم ضربه‌ای (مقدار خون پمپ‌شده) بدون تغییر باقی می‌ماند.[۵] در این مدت، تقریباً ۵۰ تا ۷۰ درصد جریان خون بدن از مرکز به پوست منتقل می‌شود تا تعریق تسهیل شود. یک فرد به طور متوسط حدود ۰.۵ کیلوگرم عرق در طول حمام سونا از دست می‌دهد.[۱۱] قرار گرفتن در معرض گرمای شدید همچنین باعث افزایش موقت حجم کلی پلاسما می‌شود تا کاهش حجم خون مرکزی را جبران کند. این افزایش حجم پلاسما نه تنها منبع ذخیره‌ای از مایع برای تعریق فراهم می‌کند، بلکه مانند آب در رادیاتور ماشین عمل کرده و بدن را خنک می‌کند تا از افزایش سریع دمای مرکزی بدن جلوگیری کرده و تحمل گرمایی را بهبود بخشد... استفاده مکرر از سونا بدن را به گرما عادت داده و پاسخ بدن به مواجهه‌های آینده را بهینه می‌کند، که احتمالاً به دلیل پدیده بیولوژیکی شناخته‌شده به عنوان هورمسیس است. هورمسیس یک پاسخ دفاعی جبرانی پس از قرار گرفتن در معرض یک استرس خفیف است که با شدت استرس تناسبی ندارد. هورمسیس طیف وسیعی از مکانیسم‌های محافظتی را فعال می‌کند که نه تنها آسیب سلولی را ترمیم می‌کنند، بلکه از مواجهه‌های بعدی با استرس‌های مخرب‌تر نیز محافظت می‌کنند... پاسخ‌های فیزیولوژیکی به استفاده از سونا به طور قابل توجهی مشابه پاسخ‌هایی است که در طول ورزش با شدت متوسط تا شدید تجربه می‌شود.در واقع، استفاده از سونا به عنوان جایگزینی برای ورزش برای افرادی که به دلیل بیماری‌های مزمن یا محدودیت‌های جسمی قادر به انجام فعالیت بدنی نیستند، پیشنهاد شده است.
 بر اساس مقاله، چه کاری مهم است که فرد بعد از استفاده از سونا انجام دهد؟</t>
   </si>
@@ -1736,9 +1739,6 @@
 با V̇O2 = 2 لیتر در دقیقه، پیشبینی می‌شود:
 E = 10 × 2 + 35 = 55 کیلوژول در دقیقه
 بنابراین، اگر ما از معادله برای ورزشکاران مردان نظامی استفاده کنیم، پاسخ صحیحتر خواهد بود.</t>
-  </si>
-  <si>
-    <t>invalid</t>
   </si>
   <si>
     <t>در یک مولکول دو رشته ای DNA، نسبت پورین به پیریمیدین برابر است با:</t>
@@ -4416,10 +4416,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5286,7 +5289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" ht="409.6">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -5299,7 +5302,7 @@
       <c r="D29" t="s">
         <v>120</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F29" t="s">
@@ -5703,7 +5706,7 @@
         <v>201</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -5743,24 +5746,24 @@
         <v>209</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -5768,19 +5771,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -5788,19 +5791,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C54" t="s">
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -5808,19 +5811,19 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C55" t="s">
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F55" t="s">
         <v>21</v>
@@ -5828,19 +5831,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -5848,19 +5851,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C57" t="s">
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F57" t="s">
         <v>8</v>
@@ -5868,19 +5871,19 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E58" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
@@ -5888,19 +5891,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -5908,19 +5911,19 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
         <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
@@ -5928,19 +5931,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C61" t="s">
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
@@ -5948,19 +5951,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C62" t="s">
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F62" t="s">
         <v>8</v>
@@ -5968,19 +5971,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E63" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F63" t="s">
         <v>8</v>
@@ -5988,19 +5991,19 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
@@ -6008,19 +6011,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -6028,22 +6031,22 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F66" t="s">
-        <v>270</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -6503,7 +6506,7 @@
         <v>362</v>
       </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -6523,7 +6526,7 @@
         <v>366</v>
       </c>
       <c r="F90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -7103,7 +7106,7 @@
         <v>482</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -7163,7 +7166,7 @@
         <v>494</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -7283,7 +7286,7 @@
         <v>518</v>
       </c>
       <c r="F128" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -7563,7 +7566,7 @@
         <v>574</v>
       </c>
       <c r="F142" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
     </row>
     <row r="143" spans="1:6">
